--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,12 +751,189 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:17:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:17:47</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3935.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3950</v>
+      </c>
+      <c r="I4" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="K4" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>77.19</v>
+      </c>
+      <c r="M4" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1228</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.582</v>
+      </c>
+      <c r="S4" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>53.41</v>
+      </c>
+      <c r="U4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:SIEMENS26AUG3950CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:17:47</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1620.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1620</v>
+      </c>
+      <c r="I5" t="n">
+        <v>20.05</v>
+      </c>
+      <c r="J5" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="K5" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2493</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="S5" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T5" t="n">
+        <v>61.07</v>
+      </c>
+      <c r="U5" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:AUROPHARMA26AUG1620CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,6 +662,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:19:36</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -932,6 +937,273 @@
       <c r="W5" t="inlineStr">
         <is>
           <t>NSE:AUROPHARMA26AUG1620CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:19:35</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>389.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H6" t="n">
+        <v>390</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="L6" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="M6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10101</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="S6" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>58.94</v>
+      </c>
+      <c r="U6" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Metals</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:NATIONALUM26AUG390CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:19:35</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TVSMOTOR</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>4351.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4350</v>
+      </c>
+      <c r="I7" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="K7" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="L7" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="M7" t="n">
+        <v>80.37</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1402</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="U7" t="n">
+        <v>49</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:TVSMOTOR26AUG4350CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:19:36</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5696.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5700</v>
+      </c>
+      <c r="I8" t="n">
+        <v>47.75</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="K8" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="L8" t="n">
+        <v>101.26</v>
+      </c>
+      <c r="M8" t="n">
+        <v>128.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1047</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="T8" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="U8" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:HEROMOTOCO26AUG5700CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,6 +939,11 @@
           <t>NSE:AUROPHARMA26AUG1620CE</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:21:21</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1204,6 +1209,100 @@
       <c r="W8" t="inlineStr">
         <is>
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:21:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:21:21</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WAAREEENER</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>2711.6</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2700</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.31</v>
+      </c>
+      <c r="K9" t="n">
+        <v>28.66</v>
+      </c>
+      <c r="L9" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="M9" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="S9" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>55.89</v>
+      </c>
+      <c r="U9" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:WAAREEENER26AUG2700PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -850,6 +850,11 @@
           <t>NSE:SIEMENS26AUG3950CE</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:23:07</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1122,6 +1127,11 @@
           <t>NSE:TVSMOTOR26AUG4350CE</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:23:07</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1303,6 +1313,100 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:WAAREEENER26AUG2700PE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:23:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:23:07</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>806.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="H10" t="n">
+        <v>810</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="K10" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="L10" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6172</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="S10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>56.46</v>
+      </c>
+      <c r="U10" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1038,6 +1038,11 @@
           <t>NSE:NATIONALUM26AUG390CE</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:24:51</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1407,6 +1412,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>NSE:SONACOMS26AUG810CE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:24:51</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1038,11 +1038,7 @@
           <t>NSE:NATIONALUM26AUG390CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-21 09:24:51</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1318,11 +1314,6 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:WAAREEENER26AUG2700PE</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-21 09:23:07</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1038,7 +1038,6 @@
           <t>NSE:NATIONALUM26AUG390CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1314,6 +1313,16 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:WAAREEENER26AUG2700PE</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:29:59</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1419,6 +1419,101 @@
           <t>2026-08-21 09:24:51</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:31:41</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3269.9</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3280</v>
+      </c>
+      <c r="I11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K11" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="L11" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="M11" t="n">
+        <v>67.44</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2487</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="S11" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="T11" t="n">
+        <v>50.82</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:GRASIM26AUG3280CE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -756,11 +756,6 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-21 09:17:47</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1325,6 +1320,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:33:25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1508,12 +1508,11 @@
           <t>NSE:GRASIM26AUG3280CE</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:33:25</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1315,9 +1315,14 @@
           <t>2026-08-21 09:29:59</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:36:50</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -756,6 +756,16 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:40:10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -761,9 +761,14 @@
           <t>2026-08-21 09:40:10</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:42:45</t>
+        </is>
+      </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1434,11 +1434,7 @@
           <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-21 09:24:51</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1531,6 +1527,95 @@
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-21 09:33:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:53:43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>176.44</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H12" t="n">
+        <v>175</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N12" t="n">
+        <v>60975</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="S12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="U12" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:BANDHANBNK26AUG175PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1434,7 +1434,6 @@
           <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1616,6 +1615,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:BANDHANBNK26AUG175PE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-21 09:55:26</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -771,6 +771,11 @@
           <t>Target 2 Hit</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:00:30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1439,6 +1439,11 @@
           <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:15:40</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1439,11 +1439,7 @@
           <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-21 10:15:40</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,7 +1439,6 @@
           <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1628,6 +1627,101 @@
           <t>2026-08-21 09:55:26</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:23:25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>605.25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H13" t="n">
+        <v>605</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K13" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="L13" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="N13" t="n">
+        <v>6097</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="S13" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>49</v>
+      </c>
+      <c r="U13" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG605CE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1439,6 +1439,11 @@
           <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:33:16</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1716,12 +1721,6 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1721,6 +1721,101 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:34:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1103.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I14" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="M14" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3816</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>64</v>
+      </c>
+      <c r="U14" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:AUBANK26AUG1100CE</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1721,6 +1721,11 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:38:11</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1810,12 +1815,6 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1439,6 +1439,16 @@
           <t>NSE:SONACOMS26AUG810CE</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:38:45</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>2026-08-21 11:33:16</t>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1825,6 +1825,101 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:39:48</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>403.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H15" t="n">
+        <v>400</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15873</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="S15" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="U15" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>NSE:KOTAKBANK26AUG400CE</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1914,12 +1914,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:43:15</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1914,11 +1914,7 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-21 11:43:15</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1914,7 +1914,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:46:30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1914,11 +1914,7 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-21 11:46:30</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1914,7 +1914,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:53:02</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1449,11 +1449,7 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-08-21 11:33:16</t>
-        </is>
-      </c>
+      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1917,6 +1913,95 @@
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-21 11:53:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:56:17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LAURUSLABS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1797.6</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="L16" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5917</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R16" t="n">
+        <v>0.834</v>
+      </c>
+      <c r="S16" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="U16" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1449,7 +1449,6 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1821,6 +1820,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2026-08-21 11:57:57</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1908,11 +1912,6 @@
       <c r="W15" t="inlineStr">
         <is>
           <t>NSE:KOTAKBANK26AUG400CE</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-21 11:53:02</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1449,6 +1449,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:04:30</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2008,6 +2008,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:09:23</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2008,11 +2008,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 12:09:23</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1919,6 +1919,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:15:54</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2008,7 +2013,6 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2013,6 +2013,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:17:31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC16"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2018,6 +2018,101 @@
           <t>2026-08-21 12:17:31</t>
         </is>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:19:08</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>605</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H17" t="n">
+        <v>605</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>6097</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="S17" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>48.91</v>
+      </c>
+      <c r="U17" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG605CE</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2013,11 +2013,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 12:17:31</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2107,12 +2103,6 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2013,7 +2013,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:22:24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1919,11 +1919,7 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-21 12:15:54</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1919,7 +1919,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:29:11</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1919,11 +1919,7 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2026-08-21 12:29:11</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1919,7 +1919,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:35:41</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2107,6 +2107,11 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:38:55</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2013,11 +2013,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 12:22:24</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2013,7 +2013,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:43:48</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2101,11 +2105,6 @@
       <c r="W17" t="inlineStr">
         <is>
           <t>NSE:KALYANKJIL26AUG605CE</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2026-08-21 12:38:55</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2107,6 +2107,11 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:45:28</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -959,6 +959,16 @@
           <t>NSE:AUROPHARMA26AUG1620CE</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2026-08-21 12:47:06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
           <t>2026-08-21 09:21:21</t>
@@ -2011,11 +2021,6 @@
       <c r="W16" t="inlineStr">
         <is>
           <t>NSE:LAURUSLABS26AUG1800CE</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 12:43:48</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2117,6 +2117,101 @@
           <t>2026-08-21 12:45:28</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:07:09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>403.45</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H18" t="n">
+        <v>400</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="L18" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="N18" t="n">
+        <v>15873</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R18" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="S18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="U18" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>NSE:KOTAKBANK26AUG400CE</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,6 +2023,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:10:25</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2206,12 +2211,6 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,11 +2023,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 13:10:25</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,7 +2023,6 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2205,6 +2204,11 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>NSE:KOTAKBANK26AUG400CE</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:13:39</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,6 +2023,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:18:32</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,11 +2023,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 13:18:32</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,7 +2023,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:23:27</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,11 +2023,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 13:23:27</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,7 +2023,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:33:14</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2205,11 +2209,6 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>NSE:KOTAKBANK26AUG400CE</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2026-08-21 13:13:39</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2211,6 +2211,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:34:55</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,11 +2023,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 13:33:14</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,7 +2023,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 13:39:57</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2023,11 +2023,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 13:39:57</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2023,7 +2023,6 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2212,6 +2211,101 @@
           <t>2026-08-21 13:34:55</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:13:46</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1105</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="K19" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="L19" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="M19" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3816</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R19" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="S19" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="U19" t="n">
+        <v>26</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>NSE:AUBANK26AUG1100CE</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1063,6 +1063,16 @@
           <t>NSE:NATIONALUM26AUG390CE</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:15:31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2300,12 +2310,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:15:31</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2310,11 +2310,7 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2026-08-21 14:15:31</t>
-        </is>
-      </c>
+      <c r="AC19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2310,7 +2310,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:20:43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2310,11 +2310,7 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>2026-08-21 14:20:43</t>
-        </is>
-      </c>
+      <c r="AC19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2310,7 +2310,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:31:14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2033,6 +2033,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:41:29</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1464,9 +1464,14 @@
           <t>2026-08-21 11:38:45</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:42:38</t>
+        </is>
+      </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Target 1 Hit</t>
+          <t>Target 2 Hit</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2038,11 +2038,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 14:41:29</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2038,7 +2038,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:51:56</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2319,6 +2323,95 @@
       <c r="AC19" t="inlineStr">
         <is>
           <t>2026-08-21 14:31:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-21 14:51:56</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>605.15</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H20" t="n">
+        <v>605</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K20" t="n">
+        <v>13.84</v>
+      </c>
+      <c r="L20" t="n">
+        <v>17.23</v>
+      </c>
+      <c r="M20" t="n">
+        <v>21.74</v>
+      </c>
+      <c r="N20" t="n">
+        <v>6097</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5590000000000001</v>
+      </c>
+      <c r="S20" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="U20" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jewellery</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2412,6 +2412,100 @@
       <c r="W20" t="inlineStr">
         <is>
           <t>NSE:KALYANKJIL26AUG605CE</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:02:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:02:35</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CUMMINSIND</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5106</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5100</v>
+      </c>
+      <c r="I21" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K21" t="n">
+        <v>56.76</v>
+      </c>
+      <c r="L21" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="M21" t="n">
+        <v>97.88</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1824</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R21" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="S21" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="T21" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="U21" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Capital Goods</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NSE:CUMMINSIND26AUG5100PE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2414,11 +2414,7 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2026-08-21 15:02:35</t>
-        </is>
-      </c>
+      <c r="AC20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2414,7 +2414,11 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:06:06</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2038,11 +2038,7 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2026-08-21 14:51:56</t>
-        </is>
-      </c>
+      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC21"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2038,7 +2038,6 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2504,6 +2503,101 @@
           <t>NSE:CUMMINSIND26AUG5100PE</t>
         </is>
       </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:14:48</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1106</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I22" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="K22" t="n">
+        <v>19.45</v>
+      </c>
+      <c r="L22" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="M22" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="N22" t="n">
+        <v>3816</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R22" t="n">
+        <v>0.802</v>
+      </c>
+      <c r="S22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="U22" t="n">
+        <v>26</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>NSE:AUBANK26AUG1100CE</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2592,12 +2592,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:16:33</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -865,6 +865,16 @@
           <t>NSE:SIEMENS26AUG3950CE</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:25:44</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>SL Hit</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-21 09:23:07</t>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2513,6 +2513,11 @@
           <t>NSE:CUMMINSIND26AUG5100PE</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:26:55</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -2048,6 +2048,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:30:24</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -1672,6 +1672,16 @@
           <t>NSE:BANDHANBNK26AUG175PE</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-21 15:31:44</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
           <t>2026-08-21 09:55:26</t>

--- a/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
+++ b/backend/signal_logs/2026-08-21/signals_2026-08-21.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:LODHA26AUG1260CE</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Closed up ~16.6 (+28.7% from entry)</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-21 09:19:36</t>
@@ -1172,6 +1177,11 @@
           <t>NSE:TVSMOTOR26AUG4350CE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed flat ~35.75 (+0.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-21 09:23:07</t>
@@ -1266,6 +1276,11 @@
           <t>NSE:HEROMOTOCO26AUG5700CE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed down ~45.8 (-4.1% from entry)</t>
+        </is>
+      </c>
       <c r="AC8" t="inlineStr">
         <is>
           <t>2026-08-21 09:21:21</t>
@@ -1578,6 +1593,11 @@
           <t>NSE:GRASIM26AUG3280CE</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Closed down ~17.6 (-12.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
           <t>2026-08-21 09:33:25</t>
@@ -1776,6 +1796,11 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed down ~6.9 (-15.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-21 11:38:11</t>
@@ -1870,6 +1895,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Closed down ~12.4 (-5.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>2026-08-21 11:57:57</t>
@@ -1964,6 +1994,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Closed up ~3.8 (+20.6% from entry)</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
           <t>2026-08-21 12:35:41</t>
@@ -2058,6 +2093,11 @@
           <t>NSE:LAURUSLABS26AUG1800CE</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Closed up ~9.0 (+6.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
           <t>2026-08-21 15:30:24</t>
@@ -2152,6 +2192,11 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Closed down ~7.1 (-13.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
           <t>2026-08-21 12:45:28</t>
@@ -2246,6 +2291,11 @@
           <t>NSE:KOTAKBANK26AUG400CE</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>Closed up ~3.9 (+23.8% from entry)</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
           <t>2026-08-21 13:34:55</t>
@@ -2340,6 +2390,11 @@
           <t>NSE:AUBANK26AUG1100CE</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Closed down ~11.1 (-15.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC19" t="inlineStr">
         <is>
           <t>2026-08-21 14:31:14</t>
@@ -2434,6 +2489,11 @@
           <t>NSE:KALYANKJIL26AUG605CE</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>Closed down ~6.5 (-20.7% from entry)</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>2026-08-21 15:06:06</t>
@@ -2528,6 +2588,11 @@
           <t>NSE:CUMMINSIND26AUG5100PE</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Closed down ~17.35 (-36.7% from entry)</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
           <t>2026-08-21 15:26:55</t>
@@ -2620,6 +2685,11 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>NSE:AUBANK26AUG1100CE</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>Closed down ~8.0 (-38.9% from entry)</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
